--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
   </si>
   <si>
     <t>В8973ВР</t>
@@ -101,8 +98,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -188,11 +186,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -200,9 +199,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,20 +555,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46149</v>
       </c>
       <c r="B2">
         <v>1147</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
       </c>
       <c r="F2">
         <v>29.06</v>
@@ -587,7 +586,7 @@
         <v>24.12</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -597,80 +596,80 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6">
         <v>29.06</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <v>1</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>0.82</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="6">
         <v>23.83</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="6">
         <v>24.12</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <v>0.29</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="7">
+      <c r="A8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="8">
         <v>29.06</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>1</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8">
         <v>23.83</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>24.12</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>0.29</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
@@ -134,7 +134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,12 +144,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -200,17 +194,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,16 +46,10 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В8973ВР</t>
@@ -67,19 +58,7 @@
     <t>78970155027722549</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:42:00</t>
-  </si>
-  <si>
-    <t>3232095632 3232095632</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ</t>
@@ -499,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -508,17 +487,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -552,107 +528,80 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>33.14</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H2">
+        <v>24.19</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J2">
+        <v>24.52</v>
+      </c>
+      <c r="K2">
+        <v>58680</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F3">
+        <v>25.67</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H3">
+        <v>17.46</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J3">
+        <v>17.71</v>
+      </c>
+      <c r="K3">
+        <v>58977</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>39.89</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>60.63</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>61.83</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2">
-        <v>58304</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>25.09</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3">
-        <v>0.78</v>
-      </c>
-      <c r="I3" s="1">
-        <v>19.57</v>
-      </c>
-      <c r="J3">
-        <v>0.79</v>
-      </c>
-      <c r="K3" s="1">
-        <v>19.82</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3">
-        <v>58304</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -660,82 +609,62 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:11">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:11">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B8" s="7">
-        <v>39.89</v>
+        <v>58.81</v>
       </c>
       <c r="C8" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>1.5199</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="E8" s="7">
-        <v>60.63</v>
+        <v>41.65</v>
       </c>
       <c r="F8" s="7">
-        <v>61.83</v>
+        <v>42.23</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7">
-        <v>25.09</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.78</v>
-      </c>
-      <c r="E9" s="7">
-        <v>19.57</v>
-      </c>
-      <c r="F9" s="7">
-        <v>19.82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="10">
-        <v>64.98</v>
-      </c>
-      <c r="C10" s="10">
+    <row r="9" spans="1:11">
+      <c r="A9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="10">
+        <v>58.81</v>
+      </c>
+      <c r="C9" s="10">
         <v>2</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>80.2</v>
-      </c>
-      <c r="F10" s="10">
-        <v>81.65000000000001</v>
+      <c r="D9" s="8"/>
+      <c r="E9" s="10">
+        <v>41.65</v>
+      </c>
+      <c r="F9" s="10">
+        <v>42.23</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Чайка</t>
   </si>
   <si>
@@ -59,6 +65,12 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>10:23</t>
+  </si>
+  <si>
+    <t>09:19</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ</t>
@@ -478,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -491,10 +503,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -528,22 +542,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46177</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>33.14</v>
@@ -560,25 +580,31 @@
       <c r="J2">
         <v>24.52</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
         <v>58680</v>
       </c>
+      <c r="M2">
+        <v>107393</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46184</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>25.67</v>
@@ -595,13 +621,19 @@
       <c r="J3">
         <v>17.71</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3">
         <v>58977</v>
       </c>
+      <c r="M3">
+        <v>111133</v>
+      </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -609,18 +641,18 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>7</v>
@@ -629,9 +661,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="7">
         <v>58.81</v>
@@ -649,9 +681,9 @@
         <v>42.23</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B9" s="10">
         <v>58.81</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -49,12 +49,6 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Чайка</t>
   </si>
   <si>
@@ -67,10 +61,7 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>10:23</t>
-  </si>
-  <si>
-    <t>09:19</t>
+    <t>2026-06-19 15:39:02</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ</t>
@@ -490,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -503,12 +494,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -542,166 +531,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>23.52</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>15.29</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>15.52</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46177</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2">
-        <v>33.14</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="H2">
-        <v>24.19</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="J2">
-        <v>24.52</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2">
-        <v>58680</v>
-      </c>
-      <c r="M2">
-        <v>107393</v>
+      <c r="B7" s="7">
+        <v>23.52</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.6501</v>
+      </c>
+      <c r="E7" s="7">
+        <v>15.29</v>
+      </c>
+      <c r="F7" s="7">
+        <v>15.52</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3">
-        <v>25.67</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="H3">
-        <v>17.46</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J3">
-        <v>17.71</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3">
-        <v>58977</v>
-      </c>
-      <c r="M3">
-        <v>111133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="7">
-        <v>58.81</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.7082000000000001</v>
-      </c>
-      <c r="E8" s="7">
-        <v>41.65</v>
-      </c>
-      <c r="F8" s="7">
-        <v>42.23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="10">
-        <v>58.81</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>41.65</v>
-      </c>
-      <c r="F9" s="10">
-        <v>42.23</v>
+      <c r="B8" s="10">
+        <v>23.52</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
+        <v>15.29</v>
+      </c>
+      <c r="F8" s="10">
+        <v>15.52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,13 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>В8973ВР</t>
@@ -61,7 +70,13 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-19 15:39:02</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:38:00</t>
+  </si>
+  <si>
+    <t>3233587190 3233587190</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ</t>
@@ -481,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -490,14 +505,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -531,45 +549,63 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>23.52</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2">
         <v>0.65</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>15.29</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>15.52</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <v>59230</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -577,29 +613,29 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="B7" s="7">
         <v>23.52</v>
@@ -617,9 +653,9 @@
         <v>15.52</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B8" s="10">
         <v>23.52</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ/ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1158 Варна Чайка</t>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В8973ВР</t>
@@ -70,13 +67,7 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>15:38:00</t>
-  </si>
-  <si>
-    <t>3233587190 3233587190</t>
+    <t>15:39</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ</t>
@@ -496,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -505,17 +496,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,57 +545,51 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
       </c>
       <c r="F2">
         <v>23.52</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>15.29</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>15.52</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>59230</v>
+      </c>
+      <c r="M2">
+        <v>115655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="H2">
-        <v>0.65</v>
-      </c>
-      <c r="I2" s="1">
-        <v>15.29</v>
-      </c>
-      <c r="J2">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15.52</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
-        <v>59230</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -613,29 +597,29 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:13">
       <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
         <v>23.52</v>
@@ -653,9 +637,9 @@
         <v>15.52</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" s="10">
         <v>23.52</v>
